--- a/input/工賃実績.xlsx
+++ b/input/工賃実績.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工賃実績" sheetId="1" r:id="R3f19ce546d824ab3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="2" r:id="Rdfdb306d9a3c4f5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="工賃実績" sheetId="1" r:id="R088dd0b4200b4894"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="2" r:id="R6c147d6902204def"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -50,7 +50,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="19">
+  <x:cellXfs count="22">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -96,6 +96,9 @@
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -356,7 +359,7 @@
         <x:v>46113</x:v>
       </x:c>
       <x:c r="D2" s="14" t="n">
-        <x:v>46152</x:v>
+        <x:v>46137</x:v>
       </x:c>
       <x:c r="E2" s="16" t="n">
         <x:v>25000</x:v>
@@ -364,7 +367,7 @@
       <x:c r="F2" s="11" t="str">
         <x:v>OFFICE01</x:v>
       </x:c>
-      <x:c r="G2" s="11" t="str"/>
+      <x:c r="G2" s="11"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="str">
@@ -377,7 +380,7 @@
         <x:v>46113</x:v>
       </x:c>
       <x:c r="D3" s="14" t="n">
-        <x:v>46152</x:v>
+        <x:v>46137</x:v>
       </x:c>
       <x:c r="E3" s="16" t="n">
         <x:v>21000</x:v>
@@ -385,35 +388,730 @@
       <x:c r="F3" s="11" t="str">
         <x:v>OFFICE01</x:v>
       </x:c>
-      <x:c r="G3" s="11" t="str"/>
+      <x:c r="G3" s="11"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="str">
-        <x:v>U002</x:v>
+        <x:v>U003</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
-        <x:v>佐藤 花子</x:v>
+        <x:v>鈴木 一郎</x:v>
       </x:c>
       <x:c r="C4" s="14" t="n">
         <x:v>46113</x:v>
       </x:c>
       <x:c r="D4" s="14" t="n">
-        <x:v>46152</x:v>
+        <x:v>46137</x:v>
       </x:c>
       <x:c r="E4" s="16" t="n">
-        <x:v>21000</x:v>
+        <x:v>23000</x:v>
       </x:c>
       <x:c r="F4" s="11" t="str">
         <x:v>OFFICE01</x:v>
       </x:c>
-      <x:c r="G4" s="11" t="str">
+      <x:c r="G4" s="11"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" t="str">
+        <x:v>U001</x:v>
+      </x:c>
+      <x:c r="B5" t="str">
+        <x:v>田中 太郎</x:v>
+      </x:c>
+      <x:c r="C5" s="20" t="n">
+        <x:v>46143</x:v>
+      </x:c>
+      <x:c r="D5" s="20" t="n">
+        <x:v>46167</x:v>
+      </x:c>
+      <x:c r="E5" s="21" t="n">
+        <x:v>25000</x:v>
+      </x:c>
+      <x:c r="F5" t="str">
+        <x:v>OFFICE01</x:v>
+      </x:c>
+      <x:c r="G5"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>U002</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>佐藤 花子</x:v>
+      </x:c>
+      <x:c r="C6" s="20" t="n">
+        <x:v>46143</x:v>
+      </x:c>
+      <x:c r="D6" s="20" t="n">
+        <x:v>46167</x:v>
+      </x:c>
+      <x:c r="E6" s="21" t="n">
+        <x:v>21000</x:v>
+      </x:c>
+      <x:c r="F6" t="str">
+        <x:v>OFFICE01</x:v>
+      </x:c>
+      <x:c r="G6"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>U003</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>鈴木 一郎</x:v>
+      </x:c>
+      <x:c r="C7" s="20" t="n">
+        <x:v>46143</x:v>
+      </x:c>
+      <x:c r="D7" s="20" t="n">
+        <x:v>46167</x:v>
+      </x:c>
+      <x:c r="E7" s="21" t="n">
+        <x:v>23000</x:v>
+      </x:c>
+      <x:c r="F7" t="str">
+        <x:v>OFFICE01</x:v>
+      </x:c>
+      <x:c r="G7"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>U001</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>田中 太郎</x:v>
+      </x:c>
+      <x:c r="C8" s="20" t="n">
+        <x:v>46174</x:v>
+      </x:c>
+      <x:c r="D8" s="20" t="n">
+        <x:v>46198</x:v>
+      </x:c>
+      <x:c r="E8" s="21" t="n">
+        <x:v>25000</x:v>
+      </x:c>
+      <x:c r="F8" t="str">
+        <x:v>OFFICE01</x:v>
+      </x:c>
+      <x:c r="G8"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>U002</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>佐藤 花子</x:v>
+      </x:c>
+      <x:c r="C9" s="20" t="n">
+        <x:v>46174</x:v>
+      </x:c>
+      <x:c r="D9" s="20" t="n">
+        <x:v>46198</x:v>
+      </x:c>
+      <x:c r="E9" s="21" t="n">
+        <x:v>21000</x:v>
+      </x:c>
+      <x:c r="F9" t="str">
+        <x:v>OFFICE01</x:v>
+      </x:c>
+      <x:c r="G9"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>U003</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>鈴木 一郎</x:v>
+      </x:c>
+      <x:c r="C10" s="20" t="n">
+        <x:v>46174</x:v>
+      </x:c>
+      <x:c r="D10" s="20" t="n">
+        <x:v>46198</x:v>
+      </x:c>
+      <x:c r="E10" s="21" t="n">
+        <x:v>23000</x:v>
+      </x:c>
+      <x:c r="F10" t="str">
+        <x:v>OFFICE01</x:v>
+      </x:c>
+      <x:c r="G10"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>U001</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>田中 太郎</x:v>
+      </x:c>
+      <x:c r="C11" s="20" t="n">
+        <x:v>46204</x:v>
+      </x:c>
+      <x:c r="D11" s="20" t="n">
+        <x:v>46228</x:v>
+      </x:c>
+      <x:c r="E11" s="21" t="n">
+        <x:v>25000</x:v>
+      </x:c>
+      <x:c r="F11" t="str">
+        <x:v>OFFICE01</x:v>
+      </x:c>
+      <x:c r="G11"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>U002</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>佐藤 花子</x:v>
+      </x:c>
+      <x:c r="C12" s="20" t="n">
+        <x:v>46204</x:v>
+      </x:c>
+      <x:c r="D12" s="20" t="n">
+        <x:v>46228</x:v>
+      </x:c>
+      <x:c r="E12" s="21" t="n">
+        <x:v>21000</x:v>
+      </x:c>
+      <x:c r="F12" t="str">
+        <x:v>OFFICE01</x:v>
+      </x:c>
+      <x:c r="G12"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" t="str">
+        <x:v>U003</x:v>
+      </x:c>
+      <x:c r="B13" t="str">
+        <x:v>鈴木 一郎</x:v>
+      </x:c>
+      <x:c r="C13" s="20" t="n">
+        <x:v>46204</x:v>
+      </x:c>
+      <x:c r="D13" s="20" t="n">
+        <x:v>46228</x:v>
+      </x:c>
+      <x:c r="E13" s="21" t="n">
+        <x:v>23000</x:v>
+      </x:c>
+      <x:c r="F13" t="str">
+        <x:v>OFFICE01</x:v>
+      </x:c>
+      <x:c r="G13"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>U001</x:v>
+      </x:c>
+      <x:c r="B14" t="str">
+        <x:v>田中 太郎</x:v>
+      </x:c>
+      <x:c r="C14" s="20" t="n">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="D14" s="20" t="n">
+        <x:v>46259</x:v>
+      </x:c>
+      <x:c r="E14" s="21" t="n">
+        <x:v>25000</x:v>
+      </x:c>
+      <x:c r="F14" t="str">
+        <x:v>OFFICE01</x:v>
+      </x:c>
+      <x:c r="G14"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" t="str">
+        <x:v>U002</x:v>
+      </x:c>
+      <x:c r="B15" t="str">
+        <x:v>佐藤 花子</x:v>
+      </x:c>
+      <x:c r="C15" s="20" t="n">
+        <x:v>46235</x:v>
+      </x:c>
+      <x:c r="D15" s="20" t="n">
+        <x:v>46259</x:v>
+      </x:c>
+      <x:c r="E15" s="21" t="n">
+        <x:v>21000</x:v>
+      </x:c>
+      <x:c r="F15" t="str">
+        <x:v>OFFICE01</x:v>
+      </x:c>
+      <x:c r="G15"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" t="str">
+        <x:v>U001</x:v>
+      </x:c>
+      <x:c r="B16" t="str">
+        <x:v>田中 太郎</x:v>
+      </x:c>
+      <x:c r="C16" s="20" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="D16" s="20" t="n">
+        <x:v>46290</x:v>
+      </x:c>
+      <x:c r="E16" s="21" t="n">
+        <x:v>25000</x:v>
+      </x:c>
+      <x:c r="F16" t="str">
+        <x:v>OFFICE01</x:v>
+      </x:c>
+      <x:c r="G16"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" t="str">
+        <x:v>U002</x:v>
+      </x:c>
+      <x:c r="B17" t="str">
+        <x:v>佐藤 花子</x:v>
+      </x:c>
+      <x:c r="C17" s="20" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="D17" s="20" t="n">
+        <x:v>46290</x:v>
+      </x:c>
+      <x:c r="E17" s="21" t="n">
+        <x:v>21000</x:v>
+      </x:c>
+      <x:c r="F17" t="str">
+        <x:v>OFFICE01</x:v>
+      </x:c>
+      <x:c r="G17"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" t="str">
+        <x:v>U002</x:v>
+      </x:c>
+      <x:c r="B18" t="str">
+        <x:v>佐藤 花子</x:v>
+      </x:c>
+      <x:c r="C18" s="20" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="D18" s="20" t="n">
+        <x:v>46290</x:v>
+      </x:c>
+      <x:c r="E18" s="21" t="n">
+        <x:v>21000</x:v>
+      </x:c>
+      <x:c r="F18" t="str">
+        <x:v>OFFICE01</x:v>
+      </x:c>
+      <x:c r="G18" t="str">
         <x:v>重複確認用</x:v>
       </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" t="str">
+        <x:v>U003</x:v>
+      </x:c>
+      <x:c r="B19" t="str">
+        <x:v>鈴木 一郎</x:v>
+      </x:c>
+      <x:c r="C19" s="20" t="n">
+        <x:v>46266</x:v>
+      </x:c>
+      <x:c r="D19" s="20" t="n">
+        <x:v>46290</x:v>
+      </x:c>
+      <x:c r="E19" s="21" t="n">
+        <x:v>23000</x:v>
+      </x:c>
+      <x:c r="F19" t="str">
+        <x:v>OFFICE01</x:v>
+      </x:c>
+      <x:c r="G19"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" t="str">
+        <x:v>U001</x:v>
+      </x:c>
+      <x:c r="B20" t="str">
+        <x:v>田中 太郎</x:v>
+      </x:c>
+      <x:c r="C20" s="20" t="n">
+        <x:v>46296</x:v>
+      </x:c>
+      <x:c r="D20" s="20" t="n">
+        <x:v>46320</x:v>
+      </x:c>
+      <x:c r="E20" s="21" t="n">
+        <x:v>25000</x:v>
+      </x:c>
+      <x:c r="F20" t="str">
+        <x:v>OFFICE01</x:v>
+      </x:c>
+      <x:c r="G20"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>U002</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>佐藤 花子</x:v>
+      </x:c>
+      <x:c r="C21" s="20" t="n">
+        <x:v>46296</x:v>
+      </x:c>
+      <x:c r="D21" s="20" t="n">
+        <x:v>46320</x:v>
+      </x:c>
+      <x:c r="E21" s="21" t="n">
+        <x:v>21000</x:v>
+      </x:c>
+      <x:c r="F21" t="str">
+        <x:v>OFFICE01</x:v>
+      </x:c>
+      <x:c r="G21"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>U003</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>鈴木 一郎</x:v>
+      </x:c>
+      <x:c r="C22" s="20" t="n">
+        <x:v>46296</x:v>
+      </x:c>
+      <x:c r="D22" s="20" t="n">
+        <x:v>46320</x:v>
+      </x:c>
+      <x:c r="E22" s="21" t="n">
+        <x:v>23000</x:v>
+      </x:c>
+      <x:c r="F22" t="str">
+        <x:v>OFFICE01</x:v>
+      </x:c>
+      <x:c r="G22"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" t="str">
+        <x:v>U001</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>田中 太郎</x:v>
+      </x:c>
+      <x:c r="C23" s="20" t="n">
+        <x:v>46327</x:v>
+      </x:c>
+      <x:c r="D23" s="20" t="n">
+        <x:v>46351</x:v>
+      </x:c>
+      <x:c r="E23" s="21" t="n">
+        <x:v>25000</x:v>
+      </x:c>
+      <x:c r="F23" t="str">
+        <x:v>OFFICE01</x:v>
+      </x:c>
+      <x:c r="G23"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" t="str">
+        <x:v>U002</x:v>
+      </x:c>
+      <x:c r="B24" t="str">
+        <x:v>佐藤 花子</x:v>
+      </x:c>
+      <x:c r="C24" s="20" t="n">
+        <x:v>46327</x:v>
+      </x:c>
+      <x:c r="D24" s="20" t="n">
+        <x:v>46351</x:v>
+      </x:c>
+      <x:c r="E24" s="21" t="n">
+        <x:v>21000</x:v>
+      </x:c>
+      <x:c r="F24" t="str">
+        <x:v>OFFICE01</x:v>
+      </x:c>
+      <x:c r="G24"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" t="str">
+        <x:v>U003</x:v>
+      </x:c>
+      <x:c r="B25" t="str">
+        <x:v>鈴木 一郎</x:v>
+      </x:c>
+      <x:c r="C25" s="20" t="n">
+        <x:v>46327</x:v>
+      </x:c>
+      <x:c r="D25" s="20" t="n">
+        <x:v>46351</x:v>
+      </x:c>
+      <x:c r="E25" s="21" t="n">
+        <x:v>23000</x:v>
+      </x:c>
+      <x:c r="F25" t="str">
+        <x:v>OFFICE01</x:v>
+      </x:c>
+      <x:c r="G25"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" t="str">
+        <x:v>U001</x:v>
+      </x:c>
+      <x:c r="B26" t="str">
+        <x:v>田中 太郎</x:v>
+      </x:c>
+      <x:c r="C26" s="20" t="n">
+        <x:v>46357</x:v>
+      </x:c>
+      <x:c r="D26" s="20" t="n">
+        <x:v>46397</x:v>
+      </x:c>
+      <x:c r="E26" s="21" t="n">
+        <x:v>25000</x:v>
+      </x:c>
+      <x:c r="F26" t="str">
+        <x:v>OFFICE01</x:v>
+      </x:c>
+      <x:c r="G26" t="str">
+        <x:v>対象月・支給月確認用</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str">
+        <x:v>U002</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>佐藤 花子</x:v>
+      </x:c>
+      <x:c r="C27" s="20" t="n">
+        <x:v>46357</x:v>
+      </x:c>
+      <x:c r="D27" s="20" t="n">
+        <x:v>46381</x:v>
+      </x:c>
+      <x:c r="E27" s="21" t="n">
+        <x:v>21000</x:v>
+      </x:c>
+      <x:c r="F27" t="str">
+        <x:v>OFFICE01</x:v>
+      </x:c>
+      <x:c r="G27"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" t="str">
+        <x:v>U003</x:v>
+      </x:c>
+      <x:c r="B28" t="str">
+        <x:v>鈴木 一郎</x:v>
+      </x:c>
+      <x:c r="C28" s="20" t="n">
+        <x:v>46357</x:v>
+      </x:c>
+      <x:c r="D28" s="20" t="n">
+        <x:v>46381</x:v>
+      </x:c>
+      <x:c r="E28" s="21" t="n">
+        <x:v>23000</x:v>
+      </x:c>
+      <x:c r="F28" t="str">
+        <x:v>OFFICE01</x:v>
+      </x:c>
+      <x:c r="G28"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" t="str">
+        <x:v>U001</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>田中 太郎</x:v>
+      </x:c>
+      <x:c r="C29" s="20" t="n">
+        <x:v>46388</x:v>
+      </x:c>
+      <x:c r="D29" s="20" t="n">
+        <x:v>46412</x:v>
+      </x:c>
+      <x:c r="E29" s="21" t="n">
+        <x:v>25000</x:v>
+      </x:c>
+      <x:c r="F29" t="str">
+        <x:v>OFFICE01</x:v>
+      </x:c>
+      <x:c r="G29"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" t="str">
+        <x:v>U002</x:v>
+      </x:c>
+      <x:c r="B30" t="str">
+        <x:v>佐藤 花子</x:v>
+      </x:c>
+      <x:c r="C30" s="20" t="n">
+        <x:v>46388</x:v>
+      </x:c>
+      <x:c r="D30" s="20" t="n">
+        <x:v>46412</x:v>
+      </x:c>
+      <x:c r="E30" s="21" t="n">
+        <x:v>21000</x:v>
+      </x:c>
+      <x:c r="F30" t="str">
+        <x:v>OFFICE01</x:v>
+      </x:c>
+      <x:c r="G30"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" t="str">
+        <x:v>U003</x:v>
+      </x:c>
+      <x:c r="B31" t="str">
+        <x:v>鈴木 一郎</x:v>
+      </x:c>
+      <x:c r="C31" s="20" t="n">
+        <x:v>46388</x:v>
+      </x:c>
+      <x:c r="D31" s="20" t="n">
+        <x:v>46412</x:v>
+      </x:c>
+      <x:c r="E31" s="21" t="n">
+        <x:v>23000</x:v>
+      </x:c>
+      <x:c r="F31" t="str">
+        <x:v>OFFICE01</x:v>
+      </x:c>
+      <x:c r="G31"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" t="str">
+        <x:v>U001</x:v>
+      </x:c>
+      <x:c r="B32" t="str">
+        <x:v>田中 太郎</x:v>
+      </x:c>
+      <x:c r="C32" s="20" t="n">
+        <x:v>46419</x:v>
+      </x:c>
+      <x:c r="D32" s="20" t="n">
+        <x:v>46443</x:v>
+      </x:c>
+      <x:c r="E32" s="21" t="n">
+        <x:v>25000</x:v>
+      </x:c>
+      <x:c r="F32" t="str">
+        <x:v>OFFICE01</x:v>
+      </x:c>
+      <x:c r="G32"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="str">
+        <x:v>U002</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>佐藤 花子</x:v>
+      </x:c>
+      <x:c r="C33" s="20" t="n">
+        <x:v>46419</x:v>
+      </x:c>
+      <x:c r="D33" s="20" t="n">
+        <x:v>46443</x:v>
+      </x:c>
+      <x:c r="E33" s="21" t="n">
+        <x:v>21000</x:v>
+      </x:c>
+      <x:c r="F33" t="str">
+        <x:v>OFFICE01</x:v>
+      </x:c>
+      <x:c r="G33"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="str">
+        <x:v>U003</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>鈴木 一郎</x:v>
+      </x:c>
+      <x:c r="C34" s="20" t="n">
+        <x:v>46419</x:v>
+      </x:c>
+      <x:c r="D34" s="20" t="n">
+        <x:v>46443</x:v>
+      </x:c>
+      <x:c r="E34" s="21" t="n">
+        <x:v>23000</x:v>
+      </x:c>
+      <x:c r="F34" t="str">
+        <x:v>OFFICE01</x:v>
+      </x:c>
+      <x:c r="G34"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" t="str">
+        <x:v>U001</x:v>
+      </x:c>
+      <x:c r="B35" t="str">
+        <x:v>田中 太郎</x:v>
+      </x:c>
+      <x:c r="C35" s="20" t="n">
+        <x:v>46447</x:v>
+      </x:c>
+      <x:c r="D35" s="20" t="n">
+        <x:v>46471</x:v>
+      </x:c>
+      <x:c r="E35" s="21" t="n">
+        <x:v>25000</x:v>
+      </x:c>
+      <x:c r="F35" t="str">
+        <x:v>OFFICE01</x:v>
+      </x:c>
+      <x:c r="G35"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" t="str">
+        <x:v>U002</x:v>
+      </x:c>
+      <x:c r="B36" t="str">
+        <x:v>佐藤 花子</x:v>
+      </x:c>
+      <x:c r="C36" s="20" t="n">
+        <x:v>46447</x:v>
+      </x:c>
+      <x:c r="D36" s="20" t="n">
+        <x:v>46471</x:v>
+      </x:c>
+      <x:c r="E36" s="21" t="n">
+        <x:v>21000</x:v>
+      </x:c>
+      <x:c r="F36" t="str">
+        <x:v>OFFICE01</x:v>
+      </x:c>
+      <x:c r="G36"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" t="str">
+        <x:v>U003</x:v>
+      </x:c>
+      <x:c r="B37" t="str">
+        <x:v>鈴木 一郎</x:v>
+      </x:c>
+      <x:c r="C37" s="20" t="n">
+        <x:v>46447</x:v>
+      </x:c>
+      <x:c r="D37" s="20" t="n">
+        <x:v>46471</x:v>
+      </x:c>
+      <x:c r="E37" s="21" t="n">
+        <x:v>23000</x:v>
+      </x:c>
+      <x:c r="F37" t="str">
+        <x:v>OFFICE01</x:v>
+      </x:c>
+      <x:c r="G37"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65af4ba6f80c45d1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23178811a2844972"/>
   </x:tableParts>
 </x:worksheet>
 </file>
